--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58446</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58167</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58627</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136626656</v>
+        <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492052</v>
+        <v>492064</v>
       </c>
       <c r="R2" t="n">
-        <v>7024677</v>
+        <v>7024653</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -799,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,56 +816,55 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136626656</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136200752</v>
+        <v>135152765</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492064</v>
+        <v>492018</v>
       </c>
       <c r="R3" t="n">
-        <v>7024653</v>
+        <v>7024683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,22 +891,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,32 +905,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -963,44 +928,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152765</v>
+        <v>135152773</v>
       </c>
       <c r="B4" t="n">
-        <v>96481</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1008,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492018</v>
+        <v>492104</v>
       </c>
       <c r="R4" t="n">
-        <v>7024683</v>
+        <v>7024702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,6 +1010,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1061,6 +1030,26 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1075,13 +1064,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152773</v>
+        <v>135152774</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1119,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492104</v>
+        <v>492073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024702</v>
+        <v>7024743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,11 +1146,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1189,12 +1173,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,13 +1195,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152774</v>
+        <v>135152775</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1255,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492073</v>
+        <v>492097</v>
       </c>
       <c r="R6" t="n">
-        <v>7024743</v>
+        <v>7024693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1342,38 +1326,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152775</v>
+        <v>135152715</v>
       </c>
       <c r="B7" t="n">
-        <v>79438</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1386,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492097</v>
+        <v>492067</v>
       </c>
       <c r="R7" t="n">
-        <v>7024693</v>
+        <v>7024791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,6 +1408,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1441,22 +1430,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,13 +1462,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152715</v>
+        <v>135152716</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1517,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492067</v>
+        <v>492005</v>
       </c>
       <c r="R8" t="n">
-        <v>7024791</v>
+        <v>7024817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1546,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,43 +1598,47 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152716</v>
+        <v>135152672</v>
       </c>
       <c r="B9" t="n">
-        <v>80553</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1653,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492005</v>
+        <v>491960</v>
       </c>
       <c r="R9" t="n">
-        <v>7024817</v>
+        <v>7024789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1693,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,12 +1706,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1728,7 +1721,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1745,13 +1738,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152672</v>
+        <v>135152673</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1793,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491960</v>
+        <v>491956</v>
       </c>
       <c r="R10" t="n">
-        <v>7024789</v>
+        <v>7024744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1831,11 +1824,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en smal rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1853,12 +1841,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1868,7 +1856,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,16 +1873,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152673</v>
+        <v>135152722</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,21 +1890,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1933,10 +1921,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491956</v>
+        <v>492095</v>
       </c>
       <c r="R11" t="n">
-        <v>7024744</v>
+        <v>7024733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2020,58 +2008,71 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152722</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492095</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024733</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2106,13 +2107,17 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2126,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2155,33 +2145,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136625386</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58003</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2198,7 +2188,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2208,14 +2198,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492057</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024734</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2242,27 +2232,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2281,7 +2261,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granskog med gott om stående död ved.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2298,16 +2278,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625386</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2315,21 +2295,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2345,7 +2325,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2359,10 +2339,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2397,11 +2377,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2414,11 +2389,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2435,16 +2405,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152663</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2452,21 +2422,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2478,7 +2448,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2488,17 +2458,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492035</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2522,17 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2546,12 +2526,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2568,65 +2543,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136625631</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>58446</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492061</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024674</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2653,27 +2622,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 1 men troligen fler.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,12 +2641,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2704,74 +2664,58 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625631</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152676</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>58415</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491978</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024717</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2795,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,92 +2753,80 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136199553</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>58167</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492073</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2918,27 +2850,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2947,12 +2869,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2969,68 +2892,62 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136625291</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>58167</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492075</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024695</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3054,27 +2971,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3083,6 +2985,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3105,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625291</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136625404</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>58627</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3122,50 +3025,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103041</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492004</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024666</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3192,27 +3087,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 1 individ hördes.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3221,6 +3101,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3243,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625404</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152777</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99186</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3260,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3292,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492109</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024714</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3330,11 +3211,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3347,7 +3223,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3364,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135471439</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>98314</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3381,41 +3257,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219815</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024690</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3439,12 +3319,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3457,30 +3342,35 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152656</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,28 +3378,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3520,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492109</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024713</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3558,11 +3448,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3575,7 +3460,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3592,16 +3477,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152736</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
-        <v>99607</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3609,21 +3494,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3641,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492090</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024764</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3708,16 +3593,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152787</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
-        <v>108287</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3725,21 +3610,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220083</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3757,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492029</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024730</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3824,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152735</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>108357</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3841,28 +3726,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3873,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491933</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024735</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3940,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152646</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3957,28 +3842,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3989,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491996</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024788</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4027,11 +3912,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4061,16 +3941,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152674</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
-        <v>99291</v>
+        <v>98285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4078,21 +3958,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>222741</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4110,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491994</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024761</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4148,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4160,7 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4177,16 +4062,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152795</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4194,21 +4079,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4226,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492072</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024744</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4279,6 +4164,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4293,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152799</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,21 +4200,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4342,10 +4232,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491940</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024802</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4395,6 +4285,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4409,16 +4304,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152803</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4426,21 +4321,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4458,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024798</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4511,6 +4406,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4525,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152814</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101478</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4542,25 +4442,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4570,14 +4478,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492106</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024668</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4604,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4622,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152780</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4658,28 +4561,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4690,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492108</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024715</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4728,11 +4631,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4745,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152781</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4779,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4811,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491956</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024753</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4864,11 +4767,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4883,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152782</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>98285</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4900,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4932,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492020</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024753</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4985,11 +4883,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -5004,16 +4897,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152783</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
-        <v>98285</v>
+        <v>101368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5021,21 +4914,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5053,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492059</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024724</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5106,11 +4999,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5125,16 +5013,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135471205</v>
+        <v>135152693</v>
       </c>
       <c r="B37" t="n">
-        <v>98309</v>
+        <v>101368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5142,50 +5030,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492009</v>
+        <v>492089</v>
       </c>
       <c r="R37" t="n">
-        <v>7024701</v>
+        <v>7024769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5212,12 +5092,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5230,30 +5110,35 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152665</v>
+        <v>135152706</v>
       </c>
       <c r="B38" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5261,28 +5146,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5293,10 +5178,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492004</v>
+        <v>491979</v>
       </c>
       <c r="R38" t="n">
-        <v>7024816</v>
+        <v>7024678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5343,12 +5228,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5364,586 +5244,6 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135152666</v>
-      </c>
-      <c r="B39" t="n">
-        <v>101380</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>491958</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7024801</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135152684</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99075</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>492050</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7024700</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135152685</v>
-      </c>
-      <c r="B41" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>492048</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7024654</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B42" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B43" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5988,11 +5288,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58167</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92107</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136626656</v>
+        <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492052</v>
+        <v>492064</v>
       </c>
       <c r="R2" t="n">
-        <v>7024677</v>
+        <v>7024653</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -799,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,56 +816,55 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136626656</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136200752</v>
+        <v>135152765</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492064</v>
+        <v>492018</v>
       </c>
       <c r="R3" t="n">
-        <v>7024653</v>
+        <v>7024683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,22 +891,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,32 +905,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -963,44 +928,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152765</v>
+        <v>135152773</v>
       </c>
       <c r="B4" t="n">
-        <v>96481</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1008,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492018</v>
+        <v>492104</v>
       </c>
       <c r="R4" t="n">
-        <v>7024683</v>
+        <v>7024702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,6 +1010,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1061,6 +1030,26 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1075,13 +1064,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152773</v>
+        <v>135152774</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1119,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492104</v>
+        <v>492073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024702</v>
+        <v>7024743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,11 +1146,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1189,12 +1173,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,13 +1195,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152774</v>
+        <v>135152775</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1255,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492073</v>
+        <v>492097</v>
       </c>
       <c r="R6" t="n">
-        <v>7024743</v>
+        <v>7024693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1342,38 +1326,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152775</v>
+        <v>135152715</v>
       </c>
       <c r="B7" t="n">
-        <v>79438</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1386,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492097</v>
+        <v>492067</v>
       </c>
       <c r="R7" t="n">
-        <v>7024693</v>
+        <v>7024791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,6 +1408,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1441,22 +1430,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,13 +1462,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152715</v>
+        <v>135152716</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1517,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492067</v>
+        <v>492005</v>
       </c>
       <c r="R8" t="n">
-        <v>7024791</v>
+        <v>7024817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1546,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,43 +1598,47 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152716</v>
+        <v>135152672</v>
       </c>
       <c r="B9" t="n">
-        <v>80553</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1653,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492005</v>
+        <v>491960</v>
       </c>
       <c r="R9" t="n">
-        <v>7024817</v>
+        <v>7024789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1693,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,12 +1706,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1728,7 +1721,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1745,13 +1738,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152672</v>
+        <v>135152673</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1793,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491960</v>
+        <v>491956</v>
       </c>
       <c r="R10" t="n">
-        <v>7024789</v>
+        <v>7024744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1831,11 +1824,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en smal rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1853,12 +1841,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1868,7 +1856,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,16 +1873,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152673</v>
+        <v>135152722</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,21 +1890,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1933,10 +1921,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491956</v>
+        <v>492095</v>
       </c>
       <c r="R11" t="n">
-        <v>7024744</v>
+        <v>7024733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2020,58 +2008,71 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152722</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492095</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024733</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2106,13 +2107,17 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2126,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2155,33 +2145,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136625386</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2198,7 +2188,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2208,14 +2198,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492057</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024734</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2242,27 +2232,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2281,7 +2261,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granskog med gott om stående död ved.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2298,16 +2278,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625386</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2315,21 +2295,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2345,7 +2325,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2359,10 +2339,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2397,11 +2377,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2414,11 +2389,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2435,16 +2405,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152663</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2452,21 +2422,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2478,7 +2448,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2488,17 +2458,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492035</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2522,17 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2546,12 +2526,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2568,65 +2543,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136625631</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>58448</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492061</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024674</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2653,27 +2622,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 1 men troligen fler.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,12 +2641,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2704,74 +2664,58 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625631</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152676</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>58415</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491978</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024717</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2795,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,92 +2753,80 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136199553</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>58169</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492073</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2918,27 +2850,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2947,12 +2869,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2969,68 +2892,62 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136625291</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492075</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024695</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3054,27 +2971,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3083,6 +2985,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3105,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625291</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136625404</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>58629</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3122,50 +3025,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103041</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492004</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024666</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3192,27 +3087,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 1 individ hördes.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3221,6 +3101,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3243,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625404</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152777</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99186</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3260,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3292,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492109</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024714</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3330,11 +3211,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3347,7 +3223,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3364,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135471439</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>98314</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3381,41 +3257,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219815</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024690</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3439,12 +3319,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3457,30 +3342,35 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152656</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,28 +3378,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3520,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492109</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024713</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3558,11 +3448,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3575,7 +3460,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3592,16 +3477,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152736</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
-        <v>99607</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3609,21 +3494,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3641,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492090</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024764</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3708,16 +3593,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152787</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
-        <v>108287</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3725,21 +3610,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220083</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3757,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492029</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024730</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3824,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152735</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>108357</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3841,28 +3726,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3873,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491933</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024735</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3940,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152646</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3957,28 +3842,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3989,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491996</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024788</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4027,11 +3912,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4061,16 +3941,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152674</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
-        <v>99291</v>
+        <v>98285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4078,21 +3958,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>222741</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4110,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491994</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024761</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4148,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4160,7 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4177,16 +4062,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152795</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4194,21 +4079,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4226,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492072</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024744</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4279,6 +4164,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4293,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152799</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,21 +4200,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4342,10 +4232,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491940</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024802</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4395,6 +4285,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4409,16 +4304,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152803</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4426,21 +4321,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4458,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024798</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4511,6 +4406,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4525,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152814</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101478</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4542,25 +4442,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4570,14 +4478,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492106</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024668</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4604,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4622,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152780</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4658,28 +4561,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4690,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492108</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024715</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4728,11 +4631,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4745,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152781</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4779,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4811,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491956</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024753</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4864,11 +4767,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4883,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152782</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>98285</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4900,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4932,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492020</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024753</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4985,11 +4883,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -5004,16 +4897,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152783</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
-        <v>98285</v>
+        <v>101368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5021,21 +4914,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5053,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492059</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024724</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5106,11 +4999,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5125,16 +5013,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135471205</v>
+        <v>135152693</v>
       </c>
       <c r="B37" t="n">
-        <v>98309</v>
+        <v>101368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5142,50 +5030,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492009</v>
+        <v>492089</v>
       </c>
       <c r="R37" t="n">
-        <v>7024701</v>
+        <v>7024769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5212,12 +5092,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5230,30 +5110,35 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152665</v>
+        <v>135152706</v>
       </c>
       <c r="B38" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5261,28 +5146,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5293,10 +5178,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492004</v>
+        <v>491979</v>
       </c>
       <c r="R38" t="n">
-        <v>7024816</v>
+        <v>7024678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5343,12 +5228,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5364,586 +5244,6 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135152666</v>
-      </c>
-      <c r="B39" t="n">
-        <v>101380</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>491958</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7024801</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135152684</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99075</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>492050</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7024700</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135152685</v>
-      </c>
-      <c r="B41" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>492048</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7024654</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B42" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B43" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5988,11 +5288,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136626656</v>
+        <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492052</v>
+        <v>492064</v>
       </c>
       <c r="R2" t="n">
-        <v>7024677</v>
+        <v>7024653</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +779,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -799,12 +794,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -821,56 +816,55 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136626656</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136200752</v>
+        <v>135152765</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492064</v>
+        <v>492018</v>
       </c>
       <c r="R3" t="n">
-        <v>7024653</v>
+        <v>7024683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,22 +891,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>20:58</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,32 +905,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -963,44 +928,43 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152765</v>
+        <v>135152773</v>
       </c>
       <c r="B4" t="n">
-        <v>96481</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2812</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1008,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492018</v>
+        <v>492104</v>
       </c>
       <c r="R4" t="n">
-        <v>7024683</v>
+        <v>7024702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1046,6 +1010,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1061,6 +1030,26 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1075,13 +1064,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152773</v>
+        <v>135152774</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1119,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492104</v>
+        <v>492073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024702</v>
+        <v>7024743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,11 +1146,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1189,12 +1173,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1211,13 +1195,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152774</v>
+        <v>135152775</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1255,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492073</v>
+        <v>492097</v>
       </c>
       <c r="R6" t="n">
-        <v>7024743</v>
+        <v>7024693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1342,38 +1326,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152775</v>
+        <v>135152715</v>
       </c>
       <c r="B7" t="n">
-        <v>79438</v>
+        <v>80553</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1386,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492097</v>
+        <v>492067</v>
       </c>
       <c r="R7" t="n">
-        <v>7024693</v>
+        <v>7024791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1424,6 +1408,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1441,22 +1430,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1473,13 +1462,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152715</v>
+        <v>135152716</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1517,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492067</v>
+        <v>492005</v>
       </c>
       <c r="R8" t="n">
-        <v>7024791</v>
+        <v>7024817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1557,7 +1546,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1609,43 +1598,47 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152716</v>
+        <v>135152672</v>
       </c>
       <c r="B9" t="n">
-        <v>80553</v>
+        <v>80558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1653,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492005</v>
+        <v>491960</v>
       </c>
       <c r="R9" t="n">
-        <v>7024817</v>
+        <v>7024789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1693,7 +1686,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>På en smal rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,12 +1706,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1728,7 +1721,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1745,13 +1738,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152672</v>
+        <v>135152673</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1793,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491960</v>
+        <v>491956</v>
       </c>
       <c r="R10" t="n">
-        <v>7024789</v>
+        <v>7024744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1831,11 +1824,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en smal rönn.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1853,12 +1841,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1868,7 +1856,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,16 +1873,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152673</v>
+        <v>135152722</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1902,21 +1890,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1933,10 +1921,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491956</v>
+        <v>492095</v>
       </c>
       <c r="R11" t="n">
-        <v>7024744</v>
+        <v>7024733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2020,58 +2008,71 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152722</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492095</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024733</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2106,13 +2107,17 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2121,24 +2126,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2155,33 +2145,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136625386</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58005</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2198,7 +2188,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2208,14 +2198,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492057</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024734</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2242,27 +2232,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2281,7 +2261,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Äldre granskog med gott om stående död ved.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2298,16 +2278,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625386</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2315,21 +2295,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2345,7 +2325,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2359,10 +2339,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2397,11 +2377,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2414,11 +2389,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2435,16 +2405,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152663</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2452,21 +2422,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2478,7 +2448,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2488,17 +2458,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492035</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2522,17 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2546,12 +2526,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2568,65 +2543,59 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136625631</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>58448</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492061</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024674</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2653,27 +2622,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Minst 1 men troligen fler.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2682,12 +2641,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2704,74 +2664,58 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625631</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152676</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>58415</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491978</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024717</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2795,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,92 +2753,80 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136199553</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>58169</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492073</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2918,27 +2850,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2947,12 +2869,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2969,68 +2892,62 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136625291</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>58169</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492075</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024695</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3054,27 +2971,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3083,6 +2985,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3105,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625291</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136625404</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>58629</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3122,50 +3025,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103041</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492004</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024666</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3192,27 +3087,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:43</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Minst 1 individ hördes.</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3221,6 +3101,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3243,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136625404</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152777</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99186</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3260,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3292,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492109</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024714</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3330,11 +3211,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3347,7 +3223,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3364,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135471439</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>98314</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3381,41 +3257,45 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219815</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024690</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3439,12 +3319,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3457,30 +3342,35 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152656</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3488,28 +3378,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3520,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492109</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024713</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3558,11 +3448,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3575,7 +3460,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3592,16 +3477,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152736</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
-        <v>99607</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3609,21 +3494,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3641,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492090</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024764</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3708,16 +3593,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152787</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
-        <v>108287</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3725,21 +3610,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220083</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3757,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492029</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024730</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3824,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152735</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>108357</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3841,28 +3726,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220102</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3873,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491933</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024735</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3940,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152646</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3957,28 +3842,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3989,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491996</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024788</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4027,11 +3912,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4061,16 +3941,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152674</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
-        <v>99291</v>
+        <v>98285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4078,21 +3958,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221952</v>
+        <v>222741</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4110,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491994</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024761</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4148,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4160,7 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4177,16 +4062,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152795</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4194,21 +4079,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4226,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492072</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024744</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4279,6 +4164,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4293,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152799</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4310,21 +4200,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4342,10 +4232,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491940</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024802</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4395,6 +4285,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4409,16 +4304,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152803</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4426,21 +4321,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4458,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024798</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4511,6 +4406,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4525,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152814</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101478</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4542,25 +4442,33 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4570,14 +4478,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492106</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024668</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4604,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4622,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152780</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4658,28 +4561,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4690,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492108</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024715</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4728,11 +4631,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4745,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4762,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152781</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4779,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4811,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491956</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024753</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4864,11 +4767,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4883,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152782</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>98285</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4900,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222741</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4932,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492020</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024753</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4985,11 +4883,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -5004,16 +4897,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152783</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
-        <v>98285</v>
+        <v>101368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5021,21 +4914,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -5053,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492059</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024724</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5106,11 +4999,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5125,16 +5013,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135471205</v>
+        <v>135152693</v>
       </c>
       <c r="B37" t="n">
-        <v>98309</v>
+        <v>101368</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5142,50 +5030,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>224885</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492009</v>
+        <v>492089</v>
       </c>
       <c r="R37" t="n">
-        <v>7024701</v>
+        <v>7024769</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5212,12 +5092,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5230,30 +5110,35 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152665</v>
+        <v>135152706</v>
       </c>
       <c r="B38" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5261,28 +5146,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5293,10 +5178,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492004</v>
+        <v>491979</v>
       </c>
       <c r="R38" t="n">
-        <v>7024816</v>
+        <v>7024678</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5343,12 +5228,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5364,586 +5244,6 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>135152666</v>
-      </c>
-      <c r="B39" t="n">
-        <v>101380</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>222771</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Svart trolldruva</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Actaea spicata</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>491958</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7024801</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>135152684</v>
-      </c>
-      <c r="B40" t="n">
-        <v>99075</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>223049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Ormbär</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>492050</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7024700</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>135152685</v>
-      </c>
-      <c r="B41" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>492048</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7024654</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B42" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B43" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5988,11 +5288,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136200752</v>
+        <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492064</v>
+        <v>492052</v>
       </c>
       <c r="R2" t="n">
-        <v>7024653</v>
+        <v>7024677</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,22 +750,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertalet fruktkroppar i en stubbe och knäckt död nedfallen granstam.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +784,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -794,12 +799,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,55 +821,56 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136200752</t>
+          <t>https://artportalen.se/Sighting/136626656</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B3" t="n">
-        <v>96481</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R3" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +897,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,13 +921,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -928,43 +963,44 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R4" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,11 +1046,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1030,26 +1061,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1064,13 +1075,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1108,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R5" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,6 +1157,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,12 +1189,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,13 +1211,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B6" t="n">
         <v>79438</v>
@@ -1239,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R6" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1326,38 +1342,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B7" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1370,10 +1386,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R7" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1408,11 +1424,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1430,22 +1441,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1462,13 +1473,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B8" t="n">
         <v>80553</v>
@@ -1506,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R8" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1557,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,47 +1609,43 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B9" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1646,10 +1653,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R9" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1686,7 +1693,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,12 +1713,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1721,7 +1728,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1738,13 +1745,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B10" t="n">
         <v>80558</v>
@@ -1786,10 +1793,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R10" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1824,6 +1831,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1841,12 +1853,12 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1856,7 +1868,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1873,16 +1885,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1921,10 +1933,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R11" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2008,71 +2020,58 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B12" t="n">
-        <v>58006</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,17 +2106,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2126,9 +2121,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,33 +2155,33 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2188,7 +2198,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,14 +2208,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492057</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024734</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2232,17 +2242,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>En spillkråka med lockläte sågs röra sig runt i skogsbeståndet där fyndplatsen finns.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2261,7 +2281,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Äldre granskog med gott om stående död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,16 +2298,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136625386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2295,21 +2315,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2339,10 +2359,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,6 +2397,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2389,6 +2414,11 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,16 +2435,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B15" t="n">
-        <v>58169</v>
+        <v>58006</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2422,21 +2452,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2448,7 +2478,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2458,17 +2488,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2522,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2526,7 +2546,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2543,59 +2568,65 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>58461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>102999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492061</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024674</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,17 +2653,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Minst 1 men troligen fler.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,13 +2682,12 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2664,58 +2704,74 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/136625631</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2795,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2753,80 +2809,92 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>136199553</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>58169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492073</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2850,17 +2918,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2869,13 +2947,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,62 +2969,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>58182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>492075</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024695</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2971,12 +3054,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 1 individ i bitvis flerskiktad äldre granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2985,7 +3083,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3008,16 +3105,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/136625291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>58642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,42 +3122,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>103041</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>492004</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024666</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3087,12 +3192,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Minst 1 individ hördes.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3101,7 +3221,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3243,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/136625404</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152777</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3260,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>492109</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3211,6 +3330,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3223,7 +3347,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3240,16 +3364,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135471439</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>98314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,45 +3381,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219815</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024690</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3319,17 +3439,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3342,35 +3457,30 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152656</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,28 +3488,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -3410,10 +3520,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>492109</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3448,6 +3558,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3575,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3477,16 +3592,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152736</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>99607</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,21 +3609,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3526,10 +3641,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492090</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,16 +3708,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152787</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>108287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3610,21 +3725,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220083</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3642,10 +3757,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492029</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024730</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3824,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152735</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>108357</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,28 +3841,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>220102</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3758,10 +3873,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491933</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3825,16 +3940,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152646</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,28 +3957,28 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3874,10 +3989,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491996</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024788</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3912,6 +4027,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3941,16 +4061,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152674</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>99291</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3958,21 +4078,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222741</v>
+        <v>221952</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3990,10 +4110,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>491994</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4148,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4160,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,16 +4177,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152795</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4079,21 +4194,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4111,10 +4226,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492072</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024744</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4164,11 +4279,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
@@ -4183,16 +4293,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135152799</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4200,21 +4310,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4232,10 +4342,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>491940</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4285,11 +4395,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
@@ -4304,16 +4409,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152803</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,21 +4426,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4353,10 +4458,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024798</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4406,11 +4511,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
@@ -4425,16 +4525,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152814</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,33 +4542,25 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4478,14 +4570,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>492106</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4604,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4622,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152780</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,28 +4658,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4593,10 +4690,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492108</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024715</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4631,6 +4728,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4643,12 +4745,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4762,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152781</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4779,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4811,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>491956</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024753</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4767,6 +4864,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4781,16 +4883,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152782</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>98285</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4900,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>222741</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492020</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024753</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4883,6 +4985,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4897,16 +5004,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152783</v>
       </c>
       <c r="B36" t="n">
-        <v>101368</v>
+        <v>98285</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4914,21 +5021,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4946,10 +5053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>492059</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024724</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4999,6 +5106,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
@@ -5013,16 +5125,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135152693</v>
+        <v>135471205</v>
       </c>
       <c r="B37" t="n">
-        <v>101368</v>
+        <v>98309</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5030,42 +5142,50 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224885</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492089</v>
+        <v>492009</v>
       </c>
       <c r="R37" t="n">
-        <v>7024769</v>
+        <v>7024701</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5092,12 +5212,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5110,35 +5230,30 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135152706</v>
+        <v>135152665</v>
       </c>
       <c r="B38" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5146,28 +5261,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -5178,10 +5293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491979</v>
+        <v>492004</v>
       </c>
       <c r="R38" t="n">
-        <v>7024678</v>
+        <v>7024816</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5228,7 +5343,12 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5244,6 +5364,586 @@
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135152666</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101380</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491958</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7024801</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135152684</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99075</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7024700</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135152685</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7024654</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5288,6 +5988,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136626656</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>136625386</v>
       </c>
       <c r="B13" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>136625631</v>
       </c>
       <c r="B16" t="n">
-        <v>58461</v>
+        <v>58463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>136625291</v>
       </c>
       <c r="B19" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>136625404</v>
       </c>
       <c r="B20" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
